--- a/output/pdf_financials_xlsx/HOH.xlsx
+++ b/output/pdf_financials_xlsx/HOH.xlsx
@@ -612,10 +612,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.175</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="13">
@@ -864,10 +864,10 @@
         <v>-19.09</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.81</v>
+        <v>1.635</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.17</v>
+        <v>-4.334</v>
       </c>
     </row>
     <row r="28">
@@ -896,10 +896,10 @@
         <v>-19.09</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.81</v>
+        <v>1.635</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.17</v>
+        <v>-4.334</v>
       </c>
     </row>
     <row r="30">
@@ -912,10 +912,10 @@
         <v>-44.00645458736745</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>7.518172377985461</v>
+        <v>6.791277258566979</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-46.73839946200404</v>
+        <v>-48.5765523425241</v>
       </c>
     </row>
     <row r="31">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">

--- a/output/pdf_financials_xlsx/HOH.xlsx
+++ b/output/pdf_financials_xlsx/HOH.xlsx
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-19.09</v>
+        <v>-6.779</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>1.81</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>10.467</v>
+        <v>-1.844</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>1.047</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-19.09</v>
+        <v>-6.779</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>1.635</v>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-19.09</v>
+        <v>-6.779</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>1.635</v>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-44.00645458736745</v>
+        <v>-15.62701705855233</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>6.791277258566979</v>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-54.8297537977999</v>
+        <v>-27.2016521610857</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>57.84530386740332</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.336</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="65">
@@ -1498,13 +1498,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>4.689</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.335</v>
       </c>
     </row>
     <row r="68">
@@ -1546,13 +1546,13 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.466</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.339</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="71">
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.466</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.339</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="72">
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.748</v>
+        <v>0.282</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1.263</v>
+        <v>0.924</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.852</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="76">
@@ -1706,15 +1706,13 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>0.01531166948538294</v>
+        <v>0.02938511717806233</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.003521468032177818</v>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0144735566827125</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.003739217355892044</v>
       </c>
     </row>
     <row r="81">
@@ -2136,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="108">
@@ -2363,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
     </row>
     <row r="122">
@@ -3140,7 +3138,11 @@
           <t>Lease liabilities (Note 7(b))</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>0.466</v>
       </c>
@@ -3888,7 +3890,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -4095,7 +4101,11 @@
           <t>Share repurchases</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -4310,7 +4320,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>-8.622999999999999</v>
       </c>
@@ -4339,7 +4353,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
         <v>-2.872</v>
       </c>
@@ -4941,7 +4959,11 @@
           <t>Deferred income tax recovery (expense) (Note 16)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="n">
         <v>2.872</v>
       </c>
@@ -5681,7 +5703,11 @@
           <t>Income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E100" s="5" t="n">
         <v>1.844</v>
       </c>
